--- a/bit/比特配置文件测试.xlsx
+++ b/bit/比特配置文件测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17205"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="138">
   <si>
     <t>窗口ID</t>
   </si>
@@ -69,34 +69,34 @@
     <t>腾</t>
   </si>
   <si>
+    <t>891d56c43ce0449182bef33695a386ff</t>
+  </si>
+  <si>
+    <t>虎</t>
+  </si>
+  <si>
+    <t>墨西哥，巴西，阿根廷</t>
+  </si>
+  <si>
+    <t>23abe995037b4efeba2159a0a17df939</t>
+  </si>
+  <si>
+    <t>德德智汇</t>
+  </si>
+  <si>
+    <t>a5cb29d875e84c8580d3f68a0d658533</t>
+  </si>
+  <si>
+    <t>德德智慧</t>
+  </si>
+  <si>
+    <t>43e74c662e474a6895fe88874ac88821</t>
+  </si>
+  <si>
+    <t>跃</t>
+  </si>
+  <si>
     <t>忽略</t>
-  </si>
-  <si>
-    <t>891d56c43ce0449182bef33695a386ff</t>
-  </si>
-  <si>
-    <t>虎</t>
-  </si>
-  <si>
-    <t>墨西哥，巴西，阿根廷</t>
-  </si>
-  <si>
-    <t>23abe995037b4efeba2159a0a17df939</t>
-  </si>
-  <si>
-    <t>德德智汇</t>
-  </si>
-  <si>
-    <t>a5cb29d875e84c8580d3f68a0d658533</t>
-  </si>
-  <si>
-    <t>德德智慧</t>
-  </si>
-  <si>
-    <t>43e74c662e474a6895fe88874ac88821</t>
-  </si>
-  <si>
-    <t>跃</t>
   </si>
   <si>
     <t>22139511815a4bf588fe96d5fdafded6</t>
@@ -1451,7 +1451,6 @@
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3"/>
       <c r="D3" t="s">
         <v>10</v>
       </c>
@@ -1466,9 +1465,7 @@
       <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
+      <c r="C4"/>
       <c r="D4" t="s">
         <v>10</v>
       </c>
@@ -1478,16 +1475,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C5"/>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1495,16 +1490,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
+      <c r="C6"/>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1512,16 +1505,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
+      <c r="C7"/>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1529,16 +1520,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>11</v>
@@ -1552,10 +1543,10 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9">
         <v>12</v>
@@ -1569,10 +1560,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10">
         <v>13</v>
@@ -1586,10 +1577,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -1603,10 +1594,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12">
         <v>15</v>
@@ -1620,10 +1611,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13">
         <v>17</v>
@@ -1637,10 +1628,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14">
         <v>18</v>
@@ -1654,10 +1645,10 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>19</v>
@@ -1671,10 +1662,10 @@
         <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16">
         <v>20</v>
@@ -1688,7 +1679,7 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -1705,10 +1696,10 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18">
         <v>21</v>
@@ -1722,10 +1713,10 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <v>22</v>
@@ -1739,10 +1730,10 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>23</v>
@@ -1756,7 +1747,7 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
         <v>47</v>
@@ -1773,10 +1764,10 @@
         <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>25</v>
@@ -1790,10 +1781,10 @@
         <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23">
         <v>26</v>
@@ -1807,10 +1798,10 @@
         <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24">
         <v>27</v>
@@ -1824,10 +1815,10 @@
         <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25">
         <v>28</v>
@@ -1841,10 +1832,10 @@
         <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26">
         <v>29</v>
@@ -1858,10 +1849,10 @@
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>30</v>
@@ -1875,10 +1866,10 @@
         <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>31</v>
@@ -1892,10 +1883,10 @@
         <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29">
         <v>32</v>
@@ -1909,10 +1900,10 @@
         <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E30">
         <v>33</v>
@@ -1926,10 +1917,10 @@
         <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E31">
         <v>34</v>
@@ -1943,10 +1934,10 @@
         <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E32">
         <v>35</v>
@@ -1960,10 +1951,10 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E33">
         <v>36</v>
@@ -1977,10 +1968,10 @@
         <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E34">
         <v>37</v>
@@ -1994,10 +1985,10 @@
         <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35">
         <v>38</v>
@@ -2011,10 +2002,10 @@
         <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E36">
         <v>39</v>
@@ -2028,10 +2019,10 @@
         <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E37">
         <v>40</v>
@@ -2045,10 +2036,10 @@
         <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E38">
         <v>41</v>
@@ -2062,10 +2053,10 @@
         <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E39">
         <v>42</v>
@@ -2079,10 +2070,10 @@
         <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40">
         <v>43</v>
@@ -2096,10 +2087,10 @@
         <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E41">
         <v>44</v>
@@ -2113,10 +2104,10 @@
         <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E42">
         <v>45</v>
@@ -2130,10 +2121,10 @@
         <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E43">
         <v>46</v>
@@ -2147,10 +2138,10 @@
         <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E44">
         <v>47</v>
@@ -2164,10 +2155,10 @@
         <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E45">
         <v>48</v>
@@ -2181,10 +2172,10 @@
         <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46">
         <v>49</v>
@@ -2198,10 +2189,10 @@
         <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E47">
         <v>50</v>
@@ -2215,10 +2206,10 @@
         <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48">
         <v>51</v>
@@ -2232,10 +2223,10 @@
         <v>102</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E49">
         <v>52</v>
@@ -2249,10 +2240,10 @@
         <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E50">
         <v>53</v>
@@ -2266,10 +2257,10 @@
         <v>106</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E51">
         <v>54</v>
@@ -2283,10 +2274,10 @@
         <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E52">
         <v>55</v>
@@ -2300,10 +2291,10 @@
         <v>110</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E53">
         <v>56</v>
@@ -2317,10 +2308,10 @@
         <v>112</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E54">
         <v>57</v>
@@ -2334,10 +2325,10 @@
         <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E55">
         <v>58</v>
@@ -2351,10 +2342,10 @@
         <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E56">
         <v>59</v>
@@ -2368,10 +2359,10 @@
         <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E57">
         <v>60</v>
@@ -2385,10 +2376,10 @@
         <v>120</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E58">
         <v>61</v>
@@ -2402,10 +2393,10 @@
         <v>122</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E59">
         <v>62</v>
@@ -2419,10 +2410,10 @@
         <v>124</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E60">
         <v>63</v>
@@ -2436,7 +2427,7 @@
         <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D61" t="s">
         <v>127</v>
@@ -2453,10 +2444,10 @@
         <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E62">
         <v>65</v>
@@ -2470,10 +2461,10 @@
         <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E63">
         <v>66</v>
@@ -2487,10 +2478,10 @@
         <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E64">
         <v>67</v>
@@ -2504,10 +2495,10 @@
         <v>135</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E65">
         <v>68</v>
@@ -2521,10 +2512,10 @@
         <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E66">
         <v>69</v>
@@ -2554,7 +2545,7 @@
         <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:4">
@@ -2565,7 +2556,7 @@
         <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2576,7 +2567,7 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">

--- a/bit/比特配置文件测试.xlsx
+++ b/bit/比特配置文件测试.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="138">
   <si>
     <t>窗口ID</t>
   </si>
@@ -84,6 +84,9 @@
     <t>德德智汇</t>
   </si>
   <si>
+    <t>忽略</t>
+  </si>
+  <si>
     <t>a5cb29d875e84c8580d3f68a0d658533</t>
   </si>
   <si>
@@ -94,9 +97,6 @@
   </si>
   <si>
     <t>跃</t>
-  </si>
-  <si>
-    <t>忽略</t>
   </si>
   <si>
     <t>22139511815a4bf588fe96d5fdafded6</t>
@@ -1451,6 +1451,7 @@
       <c r="B3" t="s">
         <v>9</v>
       </c>
+      <c r="C3"/>
       <c r="D3" t="s">
         <v>10</v>
       </c>
@@ -1495,7 +1496,9 @@
       <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6"/>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
       <c r="D6" t="s">
         <v>15</v>
       </c>
@@ -1505,12 +1508,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7"/>
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
@@ -1520,13 +1525,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -1543,7 +1548,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
@@ -1560,7 +1565,7 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -1577,7 +1582,7 @@
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1594,7 +1599,7 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -1611,7 +1616,7 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -1628,7 +1633,7 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -1645,7 +1650,7 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -1662,7 +1667,7 @@
         <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
@@ -1679,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -1696,7 +1701,7 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -1713,7 +1718,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -1730,7 +1735,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
@@ -1747,7 +1752,7 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
         <v>47</v>
@@ -1764,7 +1769,7 @@
         <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -1781,7 +1786,7 @@
         <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
         <v>15</v>
@@ -1798,7 +1803,7 @@
         <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
@@ -1815,7 +1820,7 @@
         <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
@@ -1832,7 +1837,7 @@
         <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
@@ -1849,7 +1854,7 @@
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s">
         <v>15</v>
@@ -1866,7 +1871,7 @@
         <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
         <v>15</v>
@@ -1883,7 +1888,7 @@
         <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
@@ -1900,7 +1905,7 @@
         <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
         <v>15</v>
@@ -1917,7 +1922,7 @@
         <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
         <v>15</v>
@@ -1934,7 +1939,7 @@
         <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -1951,7 +1956,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
@@ -1968,7 +1973,7 @@
         <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
@@ -1985,7 +1990,7 @@
         <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2002,7 +2007,7 @@
         <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
         <v>15</v>
@@ -2019,7 +2024,7 @@
         <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
         <v>15</v>
@@ -2036,7 +2041,7 @@
         <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
         <v>15</v>
@@ -2053,7 +2058,7 @@
         <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
@@ -2070,7 +2075,7 @@
         <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
@@ -2087,7 +2092,7 @@
         <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
@@ -2104,7 +2109,7 @@
         <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
@@ -2121,7 +2126,7 @@
         <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
         <v>15</v>
@@ -2138,7 +2143,7 @@
         <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
         <v>15</v>
@@ -2155,7 +2160,7 @@
         <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
         <v>15</v>
@@ -2172,7 +2177,7 @@
         <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D46" t="s">
         <v>15</v>
@@ -2189,7 +2194,7 @@
         <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
@@ -2206,7 +2211,7 @@
         <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
@@ -2223,7 +2228,7 @@
         <v>102</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
         <v>15</v>
@@ -2240,7 +2245,7 @@
         <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
         <v>15</v>
@@ -2257,7 +2262,7 @@
         <v>106</v>
       </c>
       <c r="C51" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
@@ -2274,7 +2279,7 @@
         <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
@@ -2291,7 +2296,7 @@
         <v>110</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
         <v>15</v>
@@ -2308,7 +2313,7 @@
         <v>112</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
@@ -2325,7 +2330,7 @@
         <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -2342,7 +2347,7 @@
         <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
         <v>15</v>
@@ -2359,7 +2364,7 @@
         <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D57" t="s">
         <v>15</v>
@@ -2376,7 +2381,7 @@
         <v>120</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D58" t="s">
         <v>15</v>
@@ -2393,7 +2398,7 @@
         <v>122</v>
       </c>
       <c r="C59" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
@@ -2410,7 +2415,7 @@
         <v>124</v>
       </c>
       <c r="C60" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
@@ -2427,7 +2432,7 @@
         <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D61" t="s">
         <v>127</v>
@@ -2444,7 +2449,7 @@
         <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
@@ -2461,7 +2466,7 @@
         <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
         <v>15</v>
@@ -2478,7 +2483,7 @@
         <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
         <v>15</v>
@@ -2495,7 +2500,7 @@
         <v>135</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
         <v>15</v>
@@ -2512,7 +2517,7 @@
         <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D66" t="s">
         <v>15</v>
